--- a/cases/case_260915_report/93A/config.xlsx
+++ b/cases/case_260915_report/93A/config.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="fixed_config" sheetId="1" r:id="Ra59562646c364e46"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="search_config" sheetId="2" r:id="R63cf934fb7644cf9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="channels" sheetId="3" r:id="R3e7f2304d0e441f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="fixed_config" sheetId="1" r:id="R09f38814392941d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="search_config" sheetId="2" r:id="R431acb5cf18c418f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="channels" sheetId="3" r:id="R1b5c9658100c4d35"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2501,10 +2501,8 @@
       <x:c r="B4" s="7" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C4" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0</x:t>
-        </x:is>
+      <x:c r="C4" s="7" t="str">
+        <x:v>0:0.02:0.14</x:v>
       </x:c>
       <x:c r="D4" s="7" t="inlineStr">
         <x:is>
@@ -2526,10 +2524,8 @@
       <x:c r="B5" s="7" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">-0.1,-0.2,-0.3</x:t>
-        </x:is>
+      <x:c r="C5" s="7" t="str">
+        <x:v>-0.34:0.02:0</x:v>
       </x:c>
       <x:c r="D5" s="7" t="inlineStr">
         <x:is>
@@ -2551,10 +2547,8 @@
       <x:c r="B6" s="7" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C6" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">-0.1,0</x:t>
-        </x:is>
+      <x:c r="C6" s="7" t="str">
+        <x:v>-0.2:0.02:0</x:v>
       </x:c>
       <x:c r="D6" s="7" t="inlineStr">
         <x:is>
@@ -2576,10 +2570,8 @@
       <x:c r="B7" s="7" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">-20:2:0</x:t>
-        </x:is>
+      <x:c r="C7" s="7" t="str">
+        <x:v>-20:1:0</x:v>
       </x:c>
       <x:c r="D7" s="7" t="inlineStr">
         <x:is>
@@ -2601,10 +2593,8 @@
       <x:c r="B8" s="7" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C8" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">-6:2:0</x:t>
-        </x:is>
+      <x:c r="C8" s="7" t="str">
+        <x:v>-6:1:0</x:v>
       </x:c>
       <x:c r="D8" s="7" t="inlineStr">
         <x:is>

--- a/cases/case_260915_report/93A/config.xlsx
+++ b/cases/case_260915_report/93A/config.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="fixed_config" sheetId="1" r:id="R09f38814392941d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="search_config" sheetId="2" r:id="R431acb5cf18c418f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="channels" sheetId="3" r:id="R1b5c9658100c4d35"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="fixed_config" sheetId="1" r:id="Rc780b41712244682"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="search_config" sheetId="2" r:id="R53b92b80a6a34e0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="channels" sheetId="3" r:id="R9cce7bb20a544dbe"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -74,7 +74,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="16">
+  <x:cellXfs count="19">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0"/>
@@ -106,6 +106,20 @@
     <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyAlignment="1">
       <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
           <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
@@ -522,12 +536,12 @@
       </x:c>
     </x:row>
     <x:row r="7" s="3" customFormat="1" ht="15" customHeight="1">
-      <x:c r="A7" s="7" t="inlineStr">
+      <x:c r="A7" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">link</x:t>
         </x:is>
       </x:c>
-      <x:c r="B7" s="7" t="inlineStr">
+      <x:c r="B7" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">fb</x:t>
         </x:is>
@@ -535,24 +549,24 @@
       <x:c r="C7" s="13" t="n">
         <x:v>106250000000</x:v>
       </x:c>
-      <x:c r="D7" s="7" t="inlineStr">
+      <x:c r="D7" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Hz</x:t>
         </x:is>
       </x:c>
-      <x:c r="E7" s="7" t="inlineStr">
+      <x:c r="E7" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Signaling rate / baud rate.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="8" s="3" customFormat="1" ht="15" customHeight="1">
-      <x:c r="A8" s="7" t="inlineStr">
+      <x:c r="A8" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">link</x:t>
         </x:is>
       </x:c>
-      <x:c r="B8" s="7" t="inlineStr">
+      <x:c r="B8" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">per_ui</x:t>
         </x:is>
@@ -560,24 +574,24 @@
       <x:c r="C8" s="13" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="D8" s="7" t="inlineStr">
+      <x:c r="D8" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">samples/UI</x:t>
         </x:is>
       </x:c>
-      <x:c r="E8" s="7" t="inlineStr">
+      <x:c r="E8" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Oversampling ratio M.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="9" s="3" customFormat="1" ht="15" customHeight="1">
-      <x:c r="A9" s="7" t="inlineStr">
+      <x:c r="A9" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">link</x:t>
         </x:is>
       </x:c>
-      <x:c r="B9" s="7" t="inlineStr">
+      <x:c r="B9" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">target_df</x:t>
         </x:is>
@@ -585,24 +599,24 @@
       <x:c r="C9" s="13" t="n">
         <x:v>10000000</x:v>
       </x:c>
-      <x:c r="D9" s="7" t="inlineStr">
+      <x:c r="D9" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Hz</x:t>
         </x:is>
       </x:c>
-      <x:c r="E9" s="7" t="inlineStr">
+      <x:c r="E9" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Target frequency step.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="10" s="3" customFormat="1" ht="15" customHeight="1">
-      <x:c r="A10" s="7" t="inlineStr">
+      <x:c r="A10" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">filter</x:t>
         </x:is>
       </x:c>
-      <x:c r="B10" s="7" t="inlineStr">
+      <x:c r="B10" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">c_m3</x:t>
         </x:is>
@@ -610,24 +624,24 @@
       <x:c r="C10" s="13" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D10" s="7" t="inlineStr">
+      <x:c r="D10" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">dimensionless</x:t>
         </x:is>
       </x:c>
-      <x:c r="E10" s="7" t="inlineStr">
+      <x:c r="E10" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">TX FFE c(-3), fixed default for single run.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="11" s="3" customFormat="1" ht="15" customHeight="1">
-      <x:c r="A11" s="7" t="inlineStr">
+      <x:c r="A11" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">filter</x:t>
         </x:is>
       </x:c>
-      <x:c r="B11" s="7" t="inlineStr">
+      <x:c r="B11" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">c_m2</x:t>
         </x:is>
@@ -635,24 +649,24 @@
       <x:c r="C11" s="13" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D11" s="7" t="inlineStr">
+      <x:c r="D11" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">dimensionless</x:t>
         </x:is>
       </x:c>
-      <x:c r="E11" s="7" t="inlineStr">
+      <x:c r="E11" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">TX FFE c(-2), fixed default if no search.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="12" s="3" customFormat="1" ht="15" customHeight="1">
-      <x:c r="A12" s="7" t="inlineStr">
+      <x:c r="A12" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">filter</x:t>
         </x:is>
       </x:c>
-      <x:c r="B12" s="7" t="inlineStr">
+      <x:c r="B12" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">c_m1</x:t>
         </x:is>
@@ -660,24 +674,24 @@
       <x:c r="C12" s="13" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D12" s="7" t="inlineStr">
+      <x:c r="D12" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">dimensionless</x:t>
         </x:is>
       </x:c>
-      <x:c r="E12" s="7" t="inlineStr">
+      <x:c r="E12" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">TX FFE c(-1), fixed default if no search.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="13" s="3" customFormat="1" ht="15" customHeight="1">
-      <x:c r="A13" s="7" t="inlineStr">
+      <x:c r="A13" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">filter</x:t>
         </x:is>
       </x:c>
-      <x:c r="B13" s="7" t="inlineStr">
+      <x:c r="B13" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">c_1</x:t>
         </x:is>
@@ -685,24 +699,24 @@
       <x:c r="C13" s="13" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D13" s="7" t="inlineStr">
+      <x:c r="D13" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">dimensionless</x:t>
         </x:is>
       </x:c>
-      <x:c r="E13" s="7" t="inlineStr">
+      <x:c r="E13" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">TX FFE c(1), fixed default if no search.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="14" s="3" customFormat="1" ht="15" customHeight="1">
-      <x:c r="A14" s="7" t="inlineStr">
+      <x:c r="A14" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">filter</x:t>
         </x:is>
       </x:c>
-      <x:c r="B14" s="7" t="inlineStr">
+      <x:c r="B14" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">num_pre</x:t>
         </x:is>
@@ -710,24 +724,24 @@
       <x:c r="C14" s="13" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D14" s="7" t="inlineStr">
+      <x:c r="D14" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">tap index</x:t>
         </x:is>
       </x:c>
-      <x:c r="E14" s="7" t="inlineStr">
+      <x:c r="E14" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Main cursor index in TX FFE vector.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="15" s="3" customFormat="1" ht="15" customHeight="1">
-      <x:c r="A15" s="7" t="inlineStr">
+      <x:c r="A15" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">filter</x:t>
         </x:is>
       </x:c>
-      <x:c r="B15" s="7" t="inlineStr">
+      <x:c r="B15" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Tr</x:t>
         </x:is>
@@ -735,24 +749,24 @@
       <x:c r="C15" s="13" t="n">
         <x:v>4e-12</x:v>
       </x:c>
-      <x:c r="D15" s="7" t="inlineStr">
+      <x:c r="D15" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">s</x:t>
         </x:is>
       </x:c>
-      <x:c r="E15" s="7" t="inlineStr">
+      <x:c r="E15" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">20%-80% transition time.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="16" s="3" customFormat="1" ht="15" customHeight="1">
-      <x:c r="A16" s="7" t="inlineStr">
+      <x:c r="A16" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">filter</x:t>
         </x:is>
       </x:c>
-      <x:c r="B16" s="7" t="inlineStr">
+      <x:c r="B16" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">fr</x:t>
         </x:is>
@@ -760,24 +774,24 @@
       <x:c r="C16" s="13" t="n">
         <x:v>58437500000.00001</x:v>
       </x:c>
-      <x:c r="D16" s="7" t="inlineStr">
+      <x:c r="D16" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Hz</x:t>
         </x:is>
       </x:c>
-      <x:c r="E16" s="7" t="inlineStr">
+      <x:c r="E16" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Receiver noise-filter 3 dB bandwidth.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="17" s="3" customFormat="1" ht="15" customHeight="1">
-      <x:c r="A17" s="7" t="inlineStr">
+      <x:c r="A17" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">filter</x:t>
         </x:is>
       </x:c>
-      <x:c r="B17" s="7" t="inlineStr">
+      <x:c r="B17" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">g_DC</x:t>
         </x:is>
@@ -785,24 +799,24 @@
       <x:c r="C17" s="13" t="n">
         <x:v>-20</x:v>
       </x:c>
-      <x:c r="D17" s="7" t="inlineStr">
+      <x:c r="D17" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">dB</x:t>
         </x:is>
       </x:c>
-      <x:c r="E17" s="7" t="inlineStr">
+      <x:c r="E17" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">CTLE DC gain default if no search.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="18" s="3" customFormat="1" ht="15" customHeight="1">
-      <x:c r="A18" s="7" t="inlineStr">
+      <x:c r="A18" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">filter</x:t>
         </x:is>
       </x:c>
-      <x:c r="B18" s="7" t="inlineStr">
+      <x:c r="B18" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">g_DC2</x:t>
         </x:is>
@@ -810,24 +824,24 @@
       <x:c r="C18" s="13" t="n">
         <x:v>-6</x:v>
       </x:c>
-      <x:c r="D18" s="7" t="inlineStr">
+      <x:c r="D18" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">dB</x:t>
         </x:is>
       </x:c>
-      <x:c r="E18" s="7" t="inlineStr">
+      <x:c r="E18" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">CTLE second DC gain default if no search.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="19" s="3" customFormat="1" ht="15" customHeight="1">
-      <x:c r="A19" s="7" t="inlineStr">
+      <x:c r="A19" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">filter</x:t>
         </x:is>
       </x:c>
-      <x:c r="B19" s="7" t="inlineStr">
+      <x:c r="B19" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">f_z</x:t>
         </x:is>
@@ -835,24 +849,24 @@
       <x:c r="C19" s="13" t="n">
         <x:v>42500000000</x:v>
       </x:c>
-      <x:c r="D19" s="7" t="inlineStr">
+      <x:c r="D19" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Hz</x:t>
         </x:is>
       </x:c>
-      <x:c r="E19" s="7" t="inlineStr">
+      <x:c r="E19" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">CTLE zero frequency.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="20" s="3" customFormat="1" ht="15" customHeight="1">
-      <x:c r="A20" s="7" t="inlineStr">
+      <x:c r="A20" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">filter</x:t>
         </x:is>
       </x:c>
-      <x:c r="B20" s="7" t="inlineStr">
+      <x:c r="B20" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">f_LF</x:t>
         </x:is>
@@ -860,24 +874,24 @@
       <x:c r="C20" s="13" t="n">
         <x:v>1328125000</x:v>
       </x:c>
-      <x:c r="D20" s="7" t="inlineStr">
+      <x:c r="D20" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Hz</x:t>
         </x:is>
       </x:c>
-      <x:c r="E20" s="7" t="inlineStr">
+      <x:c r="E20" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Low-frequency pole/zero term.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="21" s="3" customFormat="1" ht="15" customHeight="1">
-      <x:c r="A21" s="7" t="inlineStr">
+      <x:c r="A21" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">filter</x:t>
         </x:is>
       </x:c>
-      <x:c r="B21" s="7" t="inlineStr">
+      <x:c r="B21" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">f_p1</x:t>
         </x:is>
@@ -885,24 +899,24 @@
       <x:c r="C21" s="13" t="n">
         <x:v>42500000000</x:v>
       </x:c>
-      <x:c r="D21" s="7" t="inlineStr">
+      <x:c r="D21" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Hz</x:t>
         </x:is>
       </x:c>
-      <x:c r="E21" s="7" t="inlineStr">
+      <x:c r="E21" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">CTLE pole 1.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="22" s="3" customFormat="1" ht="15" customHeight="1">
-      <x:c r="A22" s="7" t="inlineStr">
+      <x:c r="A22" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">filter</x:t>
         </x:is>
       </x:c>
-      <x:c r="B22" s="7" t="inlineStr">
+      <x:c r="B22" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">f_p2</x:t>
         </x:is>
@@ -910,24 +924,24 @@
       <x:c r="C22" s="13" t="n">
         <x:v>106250000000</x:v>
       </x:c>
-      <x:c r="D22" s="7" t="inlineStr">
+      <x:c r="D22" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Hz</x:t>
         </x:is>
       </x:c>
-      <x:c r="E22" s="7" t="inlineStr">
+      <x:c r="E22" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">CTLE pole 2.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="23" s="3" customFormat="1" ht="15" customHeight="1">
-      <x:c r="A23" s="7" t="inlineStr">
+      <x:c r="A23" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">filter</x:t>
         </x:is>
       </x:c>
-      <x:c r="B23" s="7" t="inlineStr">
+      <x:c r="B23" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">A_v</x:t>
         </x:is>
@@ -935,24 +949,24 @@
       <x:c r="C23" s="13" t="n">
         <x:v>0.385</x:v>
       </x:c>
-      <x:c r="D23" s="7" t="inlineStr">
+      <x:c r="D23" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V</x:t>
         </x:is>
       </x:c>
-      <x:c r="E23" s="7" t="inlineStr">
+      <x:c r="E23" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Victim pulse amplitude.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="24" s="3" customFormat="1" ht="15" customHeight="1">
-      <x:c r="A24" s="7" t="inlineStr">
+      <x:c r="A24" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">filter</x:t>
         </x:is>
       </x:c>
-      <x:c r="B24" s="7" t="inlineStr">
+      <x:c r="B24" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">A_fe</x:t>
         </x:is>
@@ -960,24 +974,24 @@
       <x:c r="C24" s="13" t="n">
         <x:v>0.385</x:v>
       </x:c>
-      <x:c r="D24" s="7" t="inlineStr">
+      <x:c r="D24" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V</x:t>
         </x:is>
       </x:c>
-      <x:c r="E24" s="7" t="inlineStr">
+      <x:c r="E24" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">FEXT aggressor pulse amplitude.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="25" s="3" customFormat="1" ht="15" customHeight="1">
-      <x:c r="A25" s="7" t="inlineStr">
+      <x:c r="A25" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">filter</x:t>
         </x:is>
       </x:c>
-      <x:c r="B25" s="7" t="inlineStr">
+      <x:c r="B25" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">A_ne</x:t>
         </x:is>
@@ -985,12 +999,12 @@
       <x:c r="C25" s="13" t="n">
         <x:v>0.481</x:v>
       </x:c>
-      <x:c r="D25" s="7" t="inlineStr">
+      <x:c r="D25" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V</x:t>
         </x:is>
       </x:c>
-      <x:c r="E25" s="7" t="inlineStr">
+      <x:c r="E25" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">NEXT aggressor pulse amplitude.</x:t>
         </x:is>
@@ -1997,12 +2011,12 @@
       </x:c>
     </x:row>
     <x:row r="66">
-      <x:c r="A66" s="7" t="inlineStr">
+      <x:c r="A66" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">dfe</x:t>
         </x:is>
       </x:c>
-      <x:c r="B66" s="7" t="inlineStr">
+      <x:c r="B66" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">N_b</x:t>
         </x:is>
@@ -2010,24 +2024,24 @@
       <x:c r="C66" s="13" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D66" s="7" t="inlineStr">
+      <x:c r="D66" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">UI/taps</x:t>
         </x:is>
       </x:c>
-      <x:c r="E66" s="7" t="inlineStr">
+      <x:c r="E66" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Fixed DFE tap count.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="67">
-      <x:c r="A67" s="7" t="inlineStr">
+      <x:c r="A67" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">dfe</x:t>
         </x:is>
       </x:c>
-      <x:c r="B67" s="7" t="inlineStr">
+      <x:c r="B67" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">b_max</x:t>
         </x:is>
@@ -2035,24 +2049,24 @@
       <x:c r="C67" s="13" t="n">
         <x:v>0.85</x:v>
       </x:c>
-      <x:c r="D67" s="7" t="inlineStr">
+      <x:c r="D67" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">dimensionless</x:t>
         </x:is>
       </x:c>
-      <x:c r="E67" s="7" t="inlineStr">
+      <x:c r="E67" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Normalized fixed DFE coefficient limit.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="68">
-      <x:c r="A68" s="7" t="inlineStr">
+      <x:c r="A68" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">impairment</x:t>
         </x:is>
       </x:c>
-      <x:c r="B68" s="7" t="inlineStr">
+      <x:c r="B68" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">R_LM</x:t>
         </x:is>
@@ -2060,24 +2074,24 @@
       <x:c r="C68" s="13" t="n">
         <x:v>0.95</x:v>
       </x:c>
-      <x:c r="D68" s="7" t="inlineStr">
+      <x:c r="D68" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">dimensionless</x:t>
         </x:is>
       </x:c>
-      <x:c r="E68" s="7" t="inlineStr">
+      <x:c r="E68" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Level separation mismatch ratio.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="69">
-      <x:c r="A69" s="7" t="inlineStr">
+      <x:c r="A69" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">impairment</x:t>
         </x:is>
       </x:c>
-      <x:c r="B69" s="7" t="inlineStr">
+      <x:c r="B69" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SNR_TX</x:t>
         </x:is>
@@ -2085,24 +2099,24 @@
       <x:c r="C69" s="13" t="n">
         <x:v>33.5</x:v>
       </x:c>
-      <x:c r="D69" s="7" t="inlineStr">
+      <x:c r="D69" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">dB</x:t>
         </x:is>
       </x:c>
-      <x:c r="E69" s="7" t="inlineStr">
+      <x:c r="E69" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Transmitter SNR.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="70">
-      <x:c r="A70" s="7" t="inlineStr">
+      <x:c r="A70" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">impairment</x:t>
         </x:is>
       </x:c>
-      <x:c r="B70" s="7" t="inlineStr">
+      <x:c r="B70" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">sigma_RJ</x:t>
         </x:is>
@@ -2110,24 +2124,24 @@
       <x:c r="C70" s="13" t="n">
         <x:v>0.01</x:v>
       </x:c>
-      <x:c r="D70" s="7" t="inlineStr">
+      <x:c r="D70" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">UI</x:t>
         </x:is>
       </x:c>
-      <x:c r="E70" s="7" t="inlineStr">
+      <x:c r="E70" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Random jitter RMS.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="71">
-      <x:c r="A71" s="7" t="inlineStr">
+      <x:c r="A71" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">impairment</x:t>
         </x:is>
       </x:c>
-      <x:c r="B71" s="7" t="inlineStr">
+      <x:c r="B71" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">A_DD</x:t>
         </x:is>
@@ -2135,24 +2149,24 @@
       <x:c r="C71" s="13" t="n">
         <x:v>0.02</x:v>
       </x:c>
-      <x:c r="D71" s="7" t="inlineStr">
+      <x:c r="D71" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">UI</x:t>
         </x:is>
       </x:c>
-      <x:c r="E71" s="7" t="inlineStr">
+      <x:c r="E71" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Dual-Dirac jitter peak.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="72">
-      <x:c r="A72" s="7" t="inlineStr">
+      <x:c r="A72" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">impairment</x:t>
         </x:is>
       </x:c>
-      <x:c r="B72" s="7" t="inlineStr">
+      <x:c r="B72" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">eta_0</x:t>
         </x:is>
@@ -2160,24 +2174,24 @@
       <x:c r="C72" s="13" t="n">
         <x:v>7.9e-18</x:v>
       </x:c>
-      <x:c r="D72" s="7" t="inlineStr">
+      <x:c r="D72" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V^2/Hz</x:t>
         </x:is>
       </x:c>
-      <x:c r="E72" s="7" t="inlineStr">
+      <x:c r="E72" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">One-sided input-referred noise spectral density. Source workbook value 7.9e-9 V^2/GHz converted to 7.9e-18 V^2/Hz.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="73">
-      <x:c r="A73" s="7" t="inlineStr">
+      <x:c r="A73" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">com</x:t>
         </x:is>
       </x:c>
-      <x:c r="B73" s="7" t="inlineStr">
+      <x:c r="B73" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">L</x:t>
         </x:is>
@@ -2185,24 +2199,24 @@
       <x:c r="C73" s="13" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D73" s="7" t="inlineStr">
+      <x:c r="D73" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">levels</x:t>
         </x:is>
       </x:c>
-      <x:c r="E73" s="7" t="inlineStr">
+      <x:c r="E73" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Number of signal levels.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="74">
-      <x:c r="A74" s="7" t="inlineStr">
+      <x:c r="A74" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">com</x:t>
         </x:is>
       </x:c>
-      <x:c r="B74" s="7" t="inlineStr">
+      <x:c r="B74" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">DER_0</x:t>
         </x:is>
@@ -2210,207 +2224,222 @@
       <x:c r="C74" s="13" t="n">
         <x:v>2e-05</x:v>
       </x:c>
-      <x:c r="D74" s="7" t="inlineStr">
+      <x:c r="D74" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">dimensionless</x:t>
         </x:is>
       </x:c>
-      <x:c r="E74" s="7" t="inlineStr">
+      <x:c r="E74" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Target detector error ratio.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="75">
-      <x:c r="A75" s="7" t="inlineStr">
+      <x:c r="A75" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">pmf</x:t>
         </x:is>
       </x:c>
-      <x:c r="B75" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">dy_override</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C75" s="13" t="str"/>
-      <x:c r="D75" s="7" t="inlineStr">
+      <x:c r="B75" s="15" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">dy_rel_As</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C75" s="13" t="n">
+        <x:v>0.001</x:v>
+      </x:c>
+      <x:c r="D75" s="15" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">dimensionless</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E75" s="15" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">PMF dy relative to As.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" s="15" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">pmf</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B76" s="15" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">dy_abs_max</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C76" s="13" t="n">
+        <x:v>1e-05</x:v>
+      </x:c>
+      <x:c r="D76" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">V</x:t>
         </x:is>
       </x:c>
-      <x:c r="E75" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Blank means derive from As.</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="76">
-      <x:c r="A76" s="7" t="inlineStr">
+      <x:c r="E76" s="15" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">PMF dy absolute maximum.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">pmf</x:t>
         </x:is>
       </x:c>
-      <x:c r="B76" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">dy_rel_As</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C76" s="13" t="n">
+      <x:c r="B77" s="15" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">tap_rel_As</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C77" s="13" t="n">
         <x:v>0.001</x:v>
       </x:c>
-      <x:c r="D76" s="7" t="inlineStr">
+      <x:c r="D77" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">dimensionless</x:t>
         </x:is>
       </x:c>
-      <x:c r="E76" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">PMF dy relative to As.</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="77">
-      <x:c r="A77" s="7" t="inlineStr">
+      <x:c r="E77" s="15" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Tap threshold relative to As.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">pmf</x:t>
         </x:is>
       </x:c>
-      <x:c r="B77" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">dy_abs_max</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C77" s="13" t="n">
-        <x:v>1e-05</x:v>
-      </x:c>
-      <x:c r="D77" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E77" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">PMF dy absolute maximum.</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="78">
-      <x:c r="A78" s="7" t="inlineStr">
+      <x:c r="B78" s="15" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">keep_mass</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C78" s="13" t="n">
+        <x:v>0.99999</x:v>
+      </x:c>
+      <x:c r="D78" s="15" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">probability</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E78" s="15" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">PMF truncation target.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">pmf</x:t>
         </x:is>
       </x:c>
-      <x:c r="B78" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">tap_abs_th_override</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C78" s="13" t="str"/>
-      <x:c r="D78" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E78" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Blank means derive from As.</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="79">
-      <x:c r="A79" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">pmf</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B79" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">tap_rel_As</x:t>
+      <x:c r="B79" s="15" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">gaussian_n_sigma</x:t>
         </x:is>
       </x:c>
       <x:c r="C79" s="13" t="n">
-        <x:v>0.001</x:v>
-      </x:c>
-      <x:c r="D79" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">dimensionless</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E79" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Tap threshold relative to As.</x:t>
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D79" s="15" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">sigma</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E79" s="15" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Gaussian PMF half span.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="80">
-      <x:c r="A80" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">pmf</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B80" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">keep_mass</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C80" s="13" t="n">
-        <x:v>0.99999</x:v>
-      </x:c>
-      <x:c r="D80" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">probability</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E80" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">PMF truncation target.</x:t>
+      <x:c r="A80" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">channel</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B80" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">missing_dc_policy</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C80" s="14" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">skrf</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D80" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">enum</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E80" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">DC handling before channel-to-LinkSegment conversion; matched to paired 178A case.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="81">
-      <x:c r="A81" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">pmf</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B81" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">gaussian_n_sigma</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C81" s="13" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D81" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">sigma</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E81" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Gaussian PMF half span.</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A81" t="str">
+        <x:v>channel</x:v>
+      </x:c>
+      <x:c r="B81" t="str">
+        <x:v>R_0</x:v>
+      </x:c>
+      <x:c r="C81" s="14" t="n">
+        <x:v>46.25</x:v>
+      </x:c>
+      <x:c r="D81" t="str">
+        <x:v>ohm</x:v>
+      </x:c>
+      <x:c r="E81" t="str">
+        <x:v>Single-ended COM reference resistance used by channel and package models.</x:v>
+      </x:c>
+      <x:c r="F81"/>
     </x:row>
     <x:row r="82">
       <x:c r="A82" t="str">
         <x:v>channel</x:v>
       </x:c>
       <x:c r="B82" t="str">
-        <x:v>missing_dc_policy</x:v>
-      </x:c>
-      <x:c r="C82" s="14" t="str">
-        <x:v>skrf</x:v>
+        <x:v>R_d_tx</x:v>
+      </x:c>
+      <x:c r="C82" s="14" t="n">
+        <x:v>46.25</x:v>
       </x:c>
       <x:c r="D82" t="str">
-        <x:v>enum</x:v>
+        <x:v>ohm</x:v>
       </x:c>
       <x:c r="E82" t="str">
-        <x:v>DC handling before channel-to-LinkSegment conversion; matched to paired 178A case.</x:v>
-      </x:c>
+        <x:v>TX die termination resistance from the selected TX package profile.</x:v>
+      </x:c>
+      <x:c r="F82"/>
     </x:row>
     <x:row r="83">
-      <x:c r="C83" s="14" t="n"/>
+      <x:c r="A83" t="str">
+        <x:v>channel</x:v>
+      </x:c>
+      <x:c r="B83" t="str">
+        <x:v>R_d_rx</x:v>
+      </x:c>
+      <x:c r="C83" s="14" t="n">
+        <x:v>46.25</x:v>
+      </x:c>
+      <x:c r="D83" t="str">
+        <x:v>ohm</x:v>
+      </x:c>
+      <x:c r="E83" t="str">
+        <x:v>RX die termination resistance from the selected RX package profile.</x:v>
+      </x:c>
+      <x:c r="F83"/>
     </x:row>
     <x:row r="84">
       <x:c r="C84" s="14" t="n"/>
@@ -2435,12 +2464,6 @@
     </x:row>
     <x:row r="91">
       <x:c r="C91" s="14" t="n"/>
-    </x:row>
-    <x:row r="92">
-      <x:c r="C92" s="14" t="n"/>
-    </x:row>
-    <x:row r="93">
-      <x:c r="C93" s="14" t="n"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2493,184 +2516,194 @@
       </x:c>
     </x:row>
     <x:row r="4" s="3" customFormat="1" ht="15" customHeight="1">
-      <x:c r="A4" s="7" t="inlineStr">
+      <x:c r="A4" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">c_m2</x:t>
         </x:is>
       </x:c>
-      <x:c r="B4" s="7" t="b">
+      <x:c r="B4" s="15" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C4" s="7" t="str">
-        <x:v>0:0.02:0.14</x:v>
-      </x:c>
-      <x:c r="D4" s="7" t="inlineStr">
+      <x:c r="C4" s="15" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">0:0.02:0.14</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D4" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">dimensionless</x:t>
         </x:is>
       </x:c>
-      <x:c r="E4" s="7" t="inlineStr">
+      <x:c r="E4" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">TX FFE c(-2). Values support start:step:stop or comma-separated list.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="5" s="3" customFormat="1" ht="15" customHeight="1">
-      <x:c r="A5" s="7" t="inlineStr">
+      <x:c r="A5" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">c_m1</x:t>
         </x:is>
       </x:c>
-      <x:c r="B5" s="7" t="b">
+      <x:c r="B5" s="15" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="7" t="str">
-        <x:v>-0.34:0.02:0</x:v>
-      </x:c>
-      <x:c r="D5" s="7" t="inlineStr">
+      <x:c r="C5" s="15" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">-0.34:0.02:0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D5" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">dimensionless</x:t>
         </x:is>
       </x:c>
-      <x:c r="E5" s="7" t="inlineStr">
+      <x:c r="E5" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">TX FFE c(-1).</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="6" s="3" customFormat="1" ht="15" customHeight="1">
-      <x:c r="A6" s="7" t="inlineStr">
+      <x:c r="A6" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">c_1</x:t>
         </x:is>
       </x:c>
-      <x:c r="B6" s="7" t="b">
+      <x:c r="B6" s="15" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C6" s="7" t="str">
-        <x:v>-0.2:0.02:0</x:v>
-      </x:c>
-      <x:c r="D6" s="7" t="inlineStr">
+      <x:c r="C6" s="15" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">-0.2:0.02:0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D6" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">dimensionless</x:t>
         </x:is>
       </x:c>
-      <x:c r="E6" s="7" t="inlineStr">
+      <x:c r="E6" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">TX FFE c(1).</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="7" s="3" customFormat="1" ht="15" customHeight="1">
-      <x:c r="A7" s="7" t="inlineStr">
+      <x:c r="A7" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">g_DC</x:t>
         </x:is>
       </x:c>
-      <x:c r="B7" s="7" t="b">
+      <x:c r="B7" s="15" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="7" t="str">
-        <x:v>-20:1:0</x:v>
-      </x:c>
-      <x:c r="D7" s="7" t="inlineStr">
+      <x:c r="C7" s="15" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">-20:1:0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D7" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">dB</x:t>
         </x:is>
       </x:c>
-      <x:c r="E7" s="7" t="inlineStr">
+      <x:c r="E7" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">CTLE DC gain.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="8" s="3" customFormat="1" ht="15" customHeight="1">
-      <x:c r="A8" s="7" t="inlineStr">
+      <x:c r="A8" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">g_DC2</x:t>
         </x:is>
       </x:c>
-      <x:c r="B8" s="7" t="b">
+      <x:c r="B8" s="15" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C8" s="7" t="str">
-        <x:v>-6:1:0</x:v>
-      </x:c>
-      <x:c r="D8" s="7" t="inlineStr">
+      <x:c r="C8" s="15" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">-6:1:0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D8" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">dB</x:t>
         </x:is>
       </x:c>
-      <x:c r="E8" s="7" t="inlineStr">
+      <x:c r="E8" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">CTLE second DC gain.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="9" s="3" customFormat="1" ht="15" customHeight="1">
-      <x:c r="A9" s="7" t="inlineStr">
+      <x:c r="A9" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">keep_top_n</x:t>
         </x:is>
       </x:c>
-      <x:c r="B9" s="7" t="b">
+      <x:c r="B9" s="15" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C9" s="7" t="n">
+      <x:c r="C9" s="15" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D9" s="7" t="inlineStr">
+      <x:c r="D9" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">count</x:t>
         </x:is>
       </x:c>
-      <x:c r="E9" s="7" t="inlineStr">
+      <x:c r="E9" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Number of successful candidate summary rows retained.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="10" s="3" customFormat="1" ht="15" customHeight="1">
-      <x:c r="A10" s="7" t="inlineStr">
+      <x:c r="A10" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">keep_all_rows</x:t>
         </x:is>
       </x:c>
-      <x:c r="B10" s="7" t="b">
+      <x:c r="B10" s="15" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C10" s="7" t="b">
+      <x:c r="C10" s="15" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D10" s="7" t="inlineStr">
+      <x:c r="D10" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">boolean</x:t>
         </x:is>
       </x:c>
-      <x:c r="E10" s="7" t="inlineStr">
+      <x:c r="E10" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">True keeps all summary rows. Usually false for full search.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="11" s="3" customFormat="1" ht="15" customHeight="1">
-      <x:c r="A11" s="7" t="inlineStr">
+      <x:c r="A11" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">continue_on_error</x:t>
         </x:is>
       </x:c>
-      <x:c r="B11" s="7" t="b">
+      <x:c r="B11" s="15" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C11" s="7" t="b">
+      <x:c r="C11" s="15" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D11" s="7" t="inlineStr">
+      <x:c r="D11" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">boolean</x:t>
         </x:is>
       </x:c>
-      <x:c r="E11" s="7" t="inlineStr">
+      <x:c r="E11" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">True stores candidate errors instead of stopping immediately.</x:t>
         </x:is>
@@ -2690,7 +2723,7 @@
     <x:col min="3" max="3" width="54.630001068115234" style="3" customWidth="1"/>
     <x:col min="4" max="4" width="8.630000114440918" style="3" customWidth="1"/>
     <x:col min="5" max="5" width="6.630000114440918" style="3" customWidth="1"/>
-    <x:col min="6" max="6" width="12.130000114440918" style="3" customWidth="1"/>
+    <x:col min="6" max="6" width="42" style="3" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="10.630000114440918" style="3" customWidth="1"/>
     <x:col min="8" max="8" width="3.380000114440918" style="3" customWidth="1"/>
     <x:col min="9" max="9" width="36.380001068115234" style="3" customWidth="1"/>
@@ -2704,238 +2737,156 @@
       </x:c>
     </x:row>
     <x:row r="3" s="3" customFormat="1" ht="15" customHeight="1">
-      <x:c r="A3" s="9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Kind</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B3" s="9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Index</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C3" s="9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">S4P Path</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D3" s="9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Port Order</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E3" s="9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">R0 Ohm</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F3" s="9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Gamma Source</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G3" s="9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Gamma Load</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H3" s="9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Use</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I3" s="9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Description</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="4" s="3" customFormat="1" ht="15" customHeight="1">
-      <x:c r="A4" s="7" t="str">
+      <x:c r="A3" s="9" t="str">
+        <x:v>Kind</x:v>
+      </x:c>
+      <x:c r="B3" s="9" t="str">
+        <x:v>Index</x:v>
+      </x:c>
+      <x:c r="C3" s="9" t="str">
+        <x:v>S4P Path</x:v>
+      </x:c>
+      <x:c r="D3" s="9" t="str">
+        <x:v>Port Order</x:v>
+      </x:c>
+      <x:c r="E3" s="9" t="str">
+        <x:v>Use</x:v>
+      </x:c>
+      <x:c r="F3" s="9" t="str">
+        <x:v>Description</x:v>
+      </x:c>
+      <x:c r="G3" s="9"/>
+      <x:c r="H3" s="9"/>
+      <x:c r="I3" s="9"/>
+    </x:row>
+    <x:row r="4" s="3" customFormat="1" ht="30" customHeight="1">
+      <x:c r="A4" s="17" t="str">
         <x:v>victim</x:v>
       </x:c>
-      <x:c r="B4" s="7" t="n">
+      <x:c r="B4" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C4" s="7" t="str">
+      <x:c r="C4" s="17" t="str">
         <x:v>../../../reference_data/COM_channel_data/C2M/kareti_3dj_elec_02_240111/PCB_host/NoSkew/pcb_hst_S4_B2B_s0nl0_Ml36_20_t.s4p</x:v>
       </x:c>
-      <x:c r="D4" s="7" t="str">
+      <x:c r="D4" s="17" t="str">
         <x:v>0,2,1,3</x:v>
       </x:c>
-      <x:c r="E4" s="7" t="n">
-        <x:v>46.25</x:v>
-      </x:c>
-      <x:c r="F4" s="7" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="7" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H4" s="15" t="b">
+      <x:c r="E4" s="18" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I4" s="7" t="str">
+      <x:c r="F4" s="17" t="str">
         <x:v>PCB host NoSkew Ml36_20 THRU</x:v>
       </x:c>
-    </x:row>
-    <x:row r="5" s="3" customFormat="1" ht="15" customHeight="1">
-      <x:c r="A5" s="7" t="str">
+      <x:c r="G4" s="15"/>
+      <x:c r="H4" s="15"/>
+      <x:c r="I4" s="15"/>
+    </x:row>
+    <x:row r="5" s="3" customFormat="1" ht="30" customHeight="1">
+      <x:c r="A5" s="17" t="str">
         <x:v>next</x:v>
       </x:c>
-      <x:c r="B5" s="7" t="n">
+      <x:c r="B5" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="7" t="str">
+      <x:c r="C5" s="17" t="str">
         <x:v>../../../reference_data/COM_channel_data/C2M/kareti_3dj_elec_02_240111/PCB_host/NoSkew/pcb_hst_S4_B2B_s0nl0_Ml36_20_n1.s4p</x:v>
       </x:c>
-      <x:c r="D5" s="7" t="str">
+      <x:c r="D5" s="17" t="str">
         <x:v>0,2,1,3</x:v>
       </x:c>
-      <x:c r="E5" s="7" t="n">
-        <x:v>46.25</x:v>
-      </x:c>
-      <x:c r="F5" s="7" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="7" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H5" s="15" t="b">
+      <x:c r="E5" s="18" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I5" s="7" t="str">
+      <x:c r="F5" s="17" t="str">
         <x:v>Power-sum NEXT; include once</x:v>
       </x:c>
-    </x:row>
-    <x:row r="6" s="3" customFormat="1" ht="15" customHeight="1">
-      <x:c r="A6" s="7" t="str">
+      <x:c r="G5" s="15"/>
+      <x:c r="H5" s="15"/>
+      <x:c r="I5" s="15"/>
+    </x:row>
+    <x:row r="6" s="3" customFormat="1" ht="30" customHeight="1">
+      <x:c r="A6" s="17" t="str">
         <x:v>fext</x:v>
       </x:c>
-      <x:c r="B6" s="7" t="n">
+      <x:c r="B6" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C6" s="7" t="str">
+      <x:c r="C6" s="17" t="str">
         <x:v>../../../reference_data/COM_channel_data/C2M/kareti_3dj_elec_02_240111/PCB_host/NoSkew/pcb_hst_S4_B2B_s0nl0_Ml36_20_f1.s4p</x:v>
       </x:c>
-      <x:c r="D6" s="7" t="str">
+      <x:c r="D6" s="17" t="str">
         <x:v>0,2,1,3</x:v>
       </x:c>
-      <x:c r="E6" s="7" t="n">
-        <x:v>46.25</x:v>
-      </x:c>
-      <x:c r="F6" s="7" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="7" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H6" s="15" t="b">
+      <x:c r="E6" s="18" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I6" s="7" t="str">
+      <x:c r="F6" s="17" t="str">
         <x:v>Power-sum FEXT; include once</x:v>
       </x:c>
-    </x:row>
-    <x:row r="7" s="3" customFormat="1" ht="15" customHeight="1">
-      <x:c r="A7" s="7"/>
-      <x:c r="B7" s="7"/>
-      <x:c r="C7" s="7"/>
-      <x:c r="D7" s="7"/>
-      <x:c r="E7" s="7"/>
-      <x:c r="F7" s="7"/>
-      <x:c r="G7" s="7"/>
-      <x:c r="H7" s="7"/>
-      <x:c r="I7" s="7"/>
-    </x:row>
-    <x:row r="8" s="3" customFormat="1" ht="15" customHeight="1">
-      <x:c r="A8" s="7"/>
-      <x:c r="B8" s="7"/>
-      <x:c r="C8" s="7"/>
-      <x:c r="D8" s="7"/>
-      <x:c r="E8" s="7"/>
-      <x:c r="F8" s="7"/>
-      <x:c r="G8" s="7"/>
-      <x:c r="H8" s="7"/>
-      <x:c r="I8" s="7"/>
-    </x:row>
-    <x:row r="9" s="3" customFormat="1" ht="15" customHeight="1">
-      <x:c r="A9" s="7"/>
-      <x:c r="B9" s="7"/>
-      <x:c r="C9" s="7"/>
-      <x:c r="D9" s="7"/>
-      <x:c r="E9" s="7"/>
-      <x:c r="F9" s="7"/>
-      <x:c r="G9" s="7"/>
-      <x:c r="H9" s="7"/>
-      <x:c r="I9" s="7"/>
-    </x:row>
-    <x:row r="10" s="3" customFormat="1" ht="15" customHeight="1">
-      <x:c r="A10" s="7"/>
-      <x:c r="B10" s="7"/>
-      <x:c r="C10" s="7"/>
-      <x:c r="D10" s="7"/>
-      <x:c r="E10" s="7"/>
-      <x:c r="F10" s="7"/>
-      <x:c r="G10" s="7"/>
-      <x:c r="H10" s="7"/>
-      <x:c r="I10" s="7"/>
-    </x:row>
-    <x:row r="11" s="3" customFormat="1" ht="15" customHeight="1">
-      <x:c r="A11" s="7"/>
-      <x:c r="B11" s="7"/>
-      <x:c r="C11" s="7"/>
-      <x:c r="D11" s="7"/>
-      <x:c r="E11" s="7"/>
-      <x:c r="F11" s="7"/>
-      <x:c r="G11" s="7"/>
-      <x:c r="H11" s="7"/>
-      <x:c r="I11" s="7"/>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12"/>
-      <x:c r="B12"/>
-      <x:c r="C12"/>
-      <x:c r="D12"/>
-      <x:c r="E12"/>
-      <x:c r="F12"/>
-      <x:c r="G12"/>
-      <x:c r="H12"/>
-      <x:c r="I12"/>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13"/>
-      <x:c r="B13"/>
-      <x:c r="C13"/>
-      <x:c r="D13"/>
-      <x:c r="E13"/>
-      <x:c r="F13"/>
-      <x:c r="G13"/>
-      <x:c r="H13"/>
-      <x:c r="I13"/>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14"/>
-      <x:c r="B14"/>
-      <x:c r="C14"/>
-      <x:c r="D14"/>
-      <x:c r="E14"/>
-      <x:c r="F14"/>
-      <x:c r="G14"/>
-      <x:c r="H14"/>
-      <x:c r="I14"/>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15"/>
-      <x:c r="B15"/>
-      <x:c r="C15"/>
-      <x:c r="D15"/>
-      <x:c r="E15"/>
-      <x:c r="F15"/>
-      <x:c r="G15"/>
-      <x:c r="H15"/>
-      <x:c r="I15"/>
-    </x:row>
+      <x:c r="G6" s="15"/>
+      <x:c r="H6" s="15"/>
+      <x:c r="I6" s="15"/>
+    </x:row>
+    <x:row r="7" s="3" customFormat="1" ht="30" customHeight="1">
+      <x:c r="A7" s="17"/>
+      <x:c r="B7" s="17"/>
+      <x:c r="C7" s="17"/>
+      <x:c r="D7" s="17"/>
+      <x:c r="E7" s="17"/>
+      <x:c r="F7" s="17"/>
+      <x:c r="G7" s="15"/>
+      <x:c r="H7" s="15"/>
+      <x:c r="I7" s="15"/>
+    </x:row>
+    <x:row r="8" s="3" customFormat="1" ht="30" customHeight="1">
+      <x:c r="A8" s="17"/>
+      <x:c r="B8" s="17"/>
+      <x:c r="C8" s="17"/>
+      <x:c r="D8" s="17"/>
+      <x:c r="E8" s="17"/>
+      <x:c r="F8" s="17"/>
+      <x:c r="G8" s="15"/>
+      <x:c r="H8" s="15"/>
+      <x:c r="I8" s="15"/>
+    </x:row>
+    <x:row r="9" s="3" customFormat="1" ht="30" customHeight="1">
+      <x:c r="A9" s="17"/>
+      <x:c r="B9" s="17"/>
+      <x:c r="C9" s="17"/>
+      <x:c r="D9" s="17"/>
+      <x:c r="E9" s="17"/>
+      <x:c r="F9" s="17"/>
+      <x:c r="G9" s="15"/>
+      <x:c r="H9" s="15"/>
+      <x:c r="I9" s="15"/>
+    </x:row>
+    <x:row r="10" s="3" customFormat="1" ht="30" customHeight="1">
+      <x:c r="A10" s="17"/>
+      <x:c r="B10" s="17"/>
+      <x:c r="C10" s="17"/>
+      <x:c r="D10" s="17"/>
+      <x:c r="E10" s="17"/>
+      <x:c r="F10" s="17"/>
+      <x:c r="G10" s="15"/>
+      <x:c r="H10" s="15"/>
+      <x:c r="I10" s="15"/>
+    </x:row>
+    <x:row r="11" s="3" customFormat="1" ht="30" customHeight="1">
+      <x:c r="A11" s="17"/>
+      <x:c r="B11" s="17"/>
+      <x:c r="C11" s="17"/>
+      <x:c r="D11" s="17"/>
+      <x:c r="E11" s="17"/>
+      <x:c r="F11" s="17"/>
+      <x:c r="G11" s="15"/>
+      <x:c r="H11" s="15"/>
+      <x:c r="I11" s="15"/>
+    </x:row>
+    <x:row r="12"/>
+    <x:row r="13"/>
+    <x:row r="14"/>
+    <x:row r="15"/>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
